--- a/mosip_master/xlsx/dynamic_field.xlsx
+++ b/mosip_master/xlsx/dynamic_field.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA-DEV\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA\Codebases\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506A6C52-9393-473D-93A5-751439A234A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35CA3B7-F19D-496B-9217-A88B9C0F8BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6723" uniqueCount="1837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6765" uniqueCount="1851">
   <si>
     <t>id</t>
   </si>
@@ -5681,6 +5681,48 @@
   </si>
   <si>
     <t>f</t>
+  </si>
+  <si>
+    <t>f6ec66d7-90f3-4ee2-a0aa-141e10575934</t>
+  </si>
+  <si>
+    <t>citizenshipTypeCop</t>
+  </si>
+  <si>
+    <t>Citizenship Type Cop</t>
+  </si>
+  <si>
+    <t>02da35d1-2da5-4bd8-ba5e-7db53e311c7e</t>
+  </si>
+  <si>
+    <t>ce277437-de25-4cd6-b770-221caebec983</t>
+  </si>
+  <si>
+    <t>54d27445-37bd-4014-a678-a3d12c23f965</t>
+  </si>
+  <si>
+    <t>318170ed-9108-418d-a671-fdae232deb6e</t>
+  </si>
+  <si>
+    <t>ef143a73-2cea-42cc-9188-aaee2d0b87e2</t>
+  </si>
+  <si>
+    <t>{"code":"ANDC","value":"Citizenship Under Article  9 to Dual Citizenship"}</t>
+  </si>
+  <si>
+    <t>{"code":"REGDC","value":"Registration to Dual Citizenship "}</t>
+  </si>
+  <si>
+    <t>{"code":"NATDC","value":"Naturalisation to Dual Citizenship"}</t>
+  </si>
+  <si>
+    <t>{"code":"BREG","value":"Birth to Registration"}</t>
+  </si>
+  <si>
+    <t>{"code":"BIDC","value":"Birth to Dual Citizenship"}</t>
+  </si>
+  <si>
+    <t>{"code":"BNAT","value":"Birth to Naturalization"}</t>
   </si>
 </sst>
 </file>
@@ -6024,13 +6066,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G983"/>
+  <dimension ref="A1:G989"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.140625" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="54.5703125" customWidth="1"/>
+    <col min="5" max="5" width="65.7109375" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="12" max="12" width="9.140625" customWidth="1"/>
   </cols>
@@ -6403,7 +6445,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10016</v>
       </c>
@@ -6426,7 +6468,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>10017</v>
       </c>
@@ -6449,7 +6491,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>10018</v>
       </c>
@@ -6472,7 +6514,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>10022</v>
       </c>
@@ -6495,7 +6537,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>10023</v>
       </c>
@@ -6587,7 +6629,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>10027</v>
       </c>
@@ -6610,7 +6652,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10028</v>
       </c>
@@ -6955,7 +6997,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>10077</v>
       </c>
@@ -6978,7 +7020,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>10078</v>
       </c>
@@ -7001,7 +7043,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>10079</v>
       </c>
@@ -7024,7 +7066,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>10080</v>
       </c>
@@ -7047,7 +7089,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>10081</v>
       </c>
@@ -7070,7 +7112,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>10021</v>
       </c>
@@ -7139,7 +7181,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>10020</v>
       </c>
@@ -7185,7 +7227,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>10084</v>
       </c>
@@ -7208,7 +7250,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>10085</v>
       </c>
@@ -7300,7 +7342,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10089</v>
       </c>
@@ -7323,7 +7365,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>10090</v>
       </c>
@@ -7346,7 +7388,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>10092</v>
       </c>
@@ -7369,7 +7411,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10093</v>
       </c>
@@ -7714,7 +7756,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10108</v>
       </c>
@@ -7737,7 +7779,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>10109</v>
       </c>
@@ -7760,7 +7802,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>10110</v>
       </c>
@@ -7783,7 +7825,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>10111</v>
       </c>
@@ -7806,7 +7848,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>10112</v>
       </c>
@@ -7852,7 +7894,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>10115</v>
       </c>
@@ -7875,7 +7917,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>10116</v>
       </c>
@@ -7967,7 +8009,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>10120</v>
       </c>
@@ -7990,7 +8032,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>10121</v>
       </c>
@@ -8036,7 +8078,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>10123</v>
       </c>
@@ -8059,7 +8101,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>10124</v>
       </c>
@@ -8125,7 +8167,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>10091</v>
       </c>
@@ -8194,7 +8236,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10083</v>
       </c>
@@ -8217,7 +8259,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>10082</v>
       </c>
@@ -8240,7 +8282,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>10113</v>
       </c>
@@ -14188,7 +14230,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>10122</v>
       </c>
@@ -14303,7 +14345,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>10114</v>
       </c>
@@ -28629,6 +28671,144 @@
         <v>11</v>
       </c>
       <c r="G983" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="984" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A984" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B984" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C984" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D984" t="s">
+        <v>9</v>
+      </c>
+      <c r="E984" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F984" t="s">
+        <v>11</v>
+      </c>
+      <c r="G984" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="985" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A985" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B985" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C985" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D985" t="s">
+        <v>9</v>
+      </c>
+      <c r="E985" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F985" t="s">
+        <v>11</v>
+      </c>
+      <c r="G985" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="986" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A986" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B986" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C986" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D986" t="s">
+        <v>9</v>
+      </c>
+      <c r="E986" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F986" t="s">
+        <v>11</v>
+      </c>
+      <c r="G986" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="987" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A987" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B987" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C987" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D987" t="s">
+        <v>9</v>
+      </c>
+      <c r="E987" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F987" t="s">
+        <v>11</v>
+      </c>
+      <c r="G987" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="988" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A988" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B988" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C988" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D988" t="s">
+        <v>9</v>
+      </c>
+      <c r="E988" t="s">
+        <v>1849</v>
+      </c>
+      <c r="F988" t="s">
+        <v>11</v>
+      </c>
+      <c r="G988" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="989" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A989" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B989" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C989" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D989" t="s">
+        <v>9</v>
+      </c>
+      <c r="E989" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F989" t="s">
+        <v>11</v>
+      </c>
+      <c r="G989" t="s">
         <v>1160</v>
       </c>
     </row>
